--- a/Descargas/Lista Final Adap Conex Mangueras.xlsx
+++ b/Descargas/Lista Final Adap Conex Mangueras.xlsx
@@ -47060,13 +47060,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{595FB5AB-AF5D-4295-B4DE-870DBF9ADE82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67B2E79A-485A-4BFD-85FD-DCE353BAEFBC}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E5C8281A-3961-4D1C-9755-29FD881B4ADF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DDE98EDA-BE3F-4676-940C-A107843BE6D2}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{36CA56DE-9022-4825-A141-6CABA4CEE275}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{518F92C3-F24C-4B65-B59D-A42DE9D662C9}"/>
 </file>